--- a/testdata/fixtures/members_valid.xlsx
+++ b/testdata/fixtures/members_valid.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t xml:space="preserve">Liste des membres Club de plongée d'exemple</t>
   </si>
@@ -73,6 +73,9 @@
     <t xml:space="preserve">Année(s)</t>
   </si>
   <si>
+    <t xml:space="preserve">Organisation</t>
+  </si>
+  <si>
     <t xml:space="preserve">31/12/2026</t>
   </si>
   <si>
@@ -128,6 +131,9 @@
   </si>
   <si>
     <t xml:space="preserve">2024, 2025, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moniteurs actifs,Membres actifs</t>
   </si>
   <si>
     <t xml:space="preserve">Petit</t>
@@ -263,58 +269,61 @@
       <c r="W4" t="s">
         <v>20</v>
       </c>
+      <c r="X4" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="V5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W5">
         <v>2026</v>
@@ -328,52 +337,55 @@
         <v>46387</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" t="s">
+        <v>31</v>
+      </c>
+      <c r="P6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S6" t="s">
+        <v>35</v>
+      </c>
+      <c r="U6" t="s">
+        <v>32</v>
+      </c>
+      <c r="V6" t="s">
         <v>36</v>
       </c>
-      <c r="G6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" t="s">
-        <v>28</v>
-      </c>
-      <c r="M6" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>32</v>
-      </c>
-      <c r="R6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S6" t="s">
-        <v>34</v>
-      </c>
-      <c r="U6" t="s">
-        <v>31</v>
-      </c>
-      <c r="V6" t="s">
-        <v>35</v>
-      </c>
       <c r="W6" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="X6" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -381,49 +393,49 @@
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="V7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -436,55 +448,55 @@
         <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="V9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -492,52 +504,52 @@
         <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="V10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W10">
         <v>2025</v>
@@ -548,52 +560,52 @@
         <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="V11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
